--- a/public/templates/Shift_Link_Temp.xlsx
+++ b/public/templates/Shift_Link_Temp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert S Ai\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert S Ai\Tech\resp\ads_front\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DA8A66-0B85-4FBC-A313-CFE59572CAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF85036-CEAA-4A53-B10E-0E26F192426B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-12680" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,75 +25,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Test1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TopcashBack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://hpanel.hostinger.com/vps</t>
-  </si>
-  <si>
-    <t>Test2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Test3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Test4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://hpanel.hostinger.com/vps222</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://hpanel.hostinger.com/vps333</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://hpanel.hostinger.com/vps444</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
+  <si>
+    <t>https://www.vrbo.com/?k_clickid=3b4eae467c5111f180d301af0a82b821&amp;CID=a_cj_100204427&amp;utm_source=aff_cj&amp;utm_medium=partner&amp;utm_campaign=FATCOUPON+TECHNOLOGY+LTD_100204427&amp;utm_content=11553823_6a50d53a4f8a3e00127b1281&amp;CJEVENT=3b4eae467c5111f180d301af0a82b821&amp;affcid=VRBO-US.NETWORK.CJ.100204427</t>
+  </si>
+  <si>
+    <t>Fatcoupon</t>
+  </si>
+  <si>
+    <t>Vrbo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Matrix</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ads_Type</t>
-  </si>
-  <si>
-    <t>Ads_Name</t>
-  </si>
-  <si>
-    <t>Platform_Name</t>
-  </si>
-  <si>
-    <t>Full_URL</t>
-  </si>
-  <si>
-    <t>Dsplay_Number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Landing_Page_URL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://hpanel.hostinger.com</t>
+  </si>
+  <si>
+    <t>https://www.vrbo.com/</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.vrbo.com/?clickref=1011lDif8kfp&amp;CID=a_ph_6&amp;utm_source=aff_ph&amp;utm_medium=partner&amp;utm_campaign=topcashback_com_1101l252&amp;utm_content=0&amp;k_clickid=1011lDif8kfp&amp;affcid=VRBO-US.DIRECT.PHG.10l16343&amp;affdtl=PHG.1011lDif8kfp.</t>
+  </si>
+  <si>
+    <t>Topcashback</t>
+  </si>
+  <si>
+    <t>Activejunky</t>
+  </si>
+  <si>
+    <t>Reynolds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.vrbo.com/?clickref=1110l4bpEsrW&amp;CID=a_ph_6&amp;utm_source=aff_ph&amp;utm_medium=partner&amp;utm_campaign=activejunky_1101l252&amp;utm_content=0&amp;k_clickid=1110l4bpEsrW&amp;affcid=VRBO-US.DIRECT.PHG.1011l104745&amp;affdtl=PHG.1110l4bpEsrW.</t>
+  </si>
+  <si>
+    <t>Mrrebates</t>
+  </si>
+  <si>
+    <t>https://www.vrbo.com/?k_clickid=aed552ea7c5211f182dc01b60a82b82c&amp;CID=a_cj_100204427&amp;utm_source=aff_cj&amp;utm_medium=partner&amp;utm_campaign=FATCOUPON+TECHNOLOGY+LTD_100204427&amp;utm_content=11553823_6a50d7a9e6d6de00168b7e29&amp;CJEVENT=aed552ea7c5211f182dc01b60a82b82c&amp;affcid=VRBO-US.NETWORK.CJ.100204427</t>
+  </si>
+  <si>
+    <t>https://www.vrbo.com/?k_clickid=a883e25a7c5211f182dc01b60a82b82c&amp;CID=a_cj_399861&amp;utm_source=aff_cj&amp;utm_medium=partner&amp;utm_campaign=Mr.+Rebates%2C+Inc._399861&amp;utm_content=10693786_115520117&amp;CJEVENT=a883e25a7c5211f182dc01b60a82b82c&amp;affcid=VRBO-US.NETWORK.CJ.399861</t>
+  </si>
+  <si>
+    <t>adsType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adsName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>platformName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fullUrl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>landingPageUrl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>displayNumber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remarks</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -101,7 +104,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,21 +119,19 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -142,17 +143,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -430,9 +429,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
     <col min="2" max="2" width="14.5546875" customWidth="1"/>
     <col min="3" max="3" width="18.109375" customWidth="1"/>
     <col min="4" max="5" width="22.21875" customWidth="1"/>
@@ -440,120 +440,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" t="s">
-        <v>0</v>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
       <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{FBED6DBD-1E0C-4920-AC6E-26DE372185A9}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{24DEC956-905E-4EF8-B119-92A3E082A7F4}"/>
-    <hyperlink ref="D5" r:id="rId3" xr:uid="{14B30626-EB6E-4FAA-9E9D-7C9792981080}"/>
-    <hyperlink ref="E2" r:id="rId4" xr:uid="{F47EE803-5A95-4FBD-9674-5B51196DF237}"/>
-    <hyperlink ref="E3" r:id="rId5" xr:uid="{276DB6BC-C073-4A1F-8CD9-2BEDA560EC03}"/>
-    <hyperlink ref="E4" r:id="rId6" xr:uid="{EC012765-BF6C-4301-B8E2-C5D1E7D021D1}"/>
-    <hyperlink ref="E5" r:id="rId7" xr:uid="{51075107-767D-4C17-82E8-BAA2FAE77456}"/>
-  </hyperlinks>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{2F350092-D409-4637-9253-A93BC350DC75}">
+      <formula1>"Normal,Matrix"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{027A47E1-F67D-417D-BAB0-F2566D3D9EAF}">
+      <formula1>"Rebatesme,Topcashback,Extrabux,Befrugal,RetailmenotHoopladoopla,Activejunky,Rakuten,Maxrebates,Fatcoupon,Mrrebates"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/templates/Shift_Link_Temp.xlsx
+++ b/public/templates/Shift_Link_Temp.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert S Ai\Tech\resp\ads_front\public\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albert S Ai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF85036-CEAA-4A53-B10E-0E26F192426B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530FF28E-18D3-472A-952A-1B333DA6F6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-12680" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$53</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,53 +28,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
-  <si>
-    <t>https://www.vrbo.com/?k_clickid=3b4eae467c5111f180d301af0a82b821&amp;CID=a_cj_100204427&amp;utm_source=aff_cj&amp;utm_medium=partner&amp;utm_campaign=FATCOUPON+TECHNOLOGY+LTD_100204427&amp;utm_content=11553823_6a50d53a4f8a3e00127b1281&amp;CJEVENT=3b4eae467c5111f180d301af0a82b821&amp;affcid=VRBO-US.NETWORK.CJ.100204427</t>
-  </si>
-  <si>
-    <t>Fatcoupon</t>
-  </si>
-  <si>
-    <t>Vrbo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Matrix</t>
   </si>
   <si>
-    <t>https://www.vrbo.com/</t>
-  </si>
-  <si>
-    <t>Lincoln</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.vrbo.com/?clickref=1011lDif8kfp&amp;CID=a_ph_6&amp;utm_source=aff_ph&amp;utm_medium=partner&amp;utm_campaign=topcashback_com_1101l252&amp;utm_content=0&amp;k_clickid=1011lDif8kfp&amp;affcid=VRBO-US.DIRECT.PHG.10l16343&amp;affdtl=PHG.1011lDif8kfp.</t>
-  </si>
-  <si>
-    <t>Topcashback</t>
-  </si>
-  <si>
-    <t>Activejunky</t>
-  </si>
-  <si>
-    <t>Reynolds</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.vrbo.com/?clickref=1110l4bpEsrW&amp;CID=a_ph_6&amp;utm_source=aff_ph&amp;utm_medium=partner&amp;utm_campaign=activejunky_1101l252&amp;utm_content=0&amp;k_clickid=1110l4bpEsrW&amp;affcid=VRBO-US.DIRECT.PHG.1011l104745&amp;affdtl=PHG.1110l4bpEsrW.</t>
-  </si>
-  <si>
-    <t>Mrrebates</t>
-  </si>
-  <si>
-    <t>https://www.vrbo.com/?k_clickid=aed552ea7c5211f182dc01b60a82b82c&amp;CID=a_cj_100204427&amp;utm_source=aff_cj&amp;utm_medium=partner&amp;utm_campaign=FATCOUPON+TECHNOLOGY+LTD_100204427&amp;utm_content=11553823_6a50d7a9e6d6de00168b7e29&amp;CJEVENT=aed552ea7c5211f182dc01b60a82b82c&amp;affcid=VRBO-US.NETWORK.CJ.100204427</t>
-  </si>
-  <si>
-    <t>https://www.vrbo.com/?k_clickid=a883e25a7c5211f182dc01b60a82b82c&amp;CID=a_cj_399861&amp;utm_source=aff_cj&amp;utm_medium=partner&amp;utm_campaign=Mr.+Rebates%2C+Inc._399861&amp;utm_content=10693786_115520117&amp;CJEVENT=a883e25a7c5211f182dc01b60a82b82c&amp;affcid=VRBO-US.NETWORK.CJ.399861</t>
-  </si>
-  <si>
     <t>adsType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -97,6 +58,22 @@
   </si>
   <si>
     <t>remarks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hotels</t>
+  </si>
+  <si>
+    <t>Retailmenot</t>
+  </si>
+  <si>
+    <t>https://www.hotels.com/?clickref=1101lDBjDMtL&amp;rffrid=aff.hcom.US.038.000.11l1030.kwrd=1101lDBjDMtL&amp;affcid=HCOM-US.DIRECT.PHG.11l1030&amp;afflid=1101lDBjDMtL&amp;affdtl=PHG.1101lDBjDMtL.&amp;affdtl=PHG.1101lDBjDMtL.</t>
+  </si>
+  <si>
+    <t>https://www.hotels.com/</t>
+  </si>
+  <si>
+    <t>Abram</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -104,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +94,14 @@
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -143,15 +128,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -429,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -441,150 +429,65 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="2"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6" t="s">
-        <v>5</v>
-      </c>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D26" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G53" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576" xr:uid="{2F350092-D409-4637-9253-A93BC350DC75}">
       <formula1>"Normal,Matrix"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{027A47E1-F67D-417D-BAB0-F2566D3D9EAF}">
-      <formula1>"Rebatesme,Topcashback,Extrabux,Befrugal,RetailmenotHoopladoopla,Activejunky,Rakuten,Maxrebates,Fatcoupon,Mrrebates"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{26DBB387-F1C2-448B-802F-AEB91ABF5DBE}">
+      <formula1>"Rebatesme,Topcashback,Extrabux,Befrugal,Retailmenot,Hoopladoopla,Activejunky,Rakuten,Maxrebates,Fatcoupon,Mrrebates"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
